--- a/day5mathfunctions.xlsx
+++ b/day5mathfunctions.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MITS\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3701DC22-AB5E-4480-B784-8BBA3475976B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E34541C6-BCB4-4B29-BAAA-8FECF67C4671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D8DD2A99-B997-4986-8C42-5D42BB7EEB32}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="190">
   <si>
     <t>Yes</t>
   </si>
@@ -523,6 +523,87 @@
   </si>
   <si>
     <t>Column1</t>
+  </si>
+  <si>
+    <t>basic formulas</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>avg</t>
+  </si>
+  <si>
+    <t>sum</t>
+  </si>
+  <si>
+    <t>left</t>
+  </si>
+  <si>
+    <t>right</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>len</t>
+  </si>
+  <si>
+    <t>median</t>
+  </si>
+  <si>
+    <t>date functions</t>
+  </si>
+  <si>
+    <t>date()</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>networkdays</t>
+  </si>
+  <si>
+    <t>weekdays</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>month</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>string functions</t>
+  </si>
+  <si>
+    <t>find</t>
+  </si>
+  <si>
+    <t>replace</t>
+  </si>
+  <si>
+    <t>substitiute</t>
+  </si>
+  <si>
+    <t>concat</t>
+  </si>
+  <si>
+    <t>search</t>
+  </si>
+  <si>
+    <t>mid</t>
+  </si>
+  <si>
+    <t>math functions</t>
+  </si>
+  <si>
+    <t>fact</t>
   </si>
 </sst>
 </file>
@@ -977,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9900C5B-8AD4-4E09-8A19-16D0F78DFD76}">
-  <dimension ref="A1:AH40"/>
+  <dimension ref="A1:AH62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" customWidth="1"/>
@@ -3718,6 +3799,141 @@
         <v>52</v>
       </c>
     </row>
+    <row r="52" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N52" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="S52" s="2"/>
+      <c r="U52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="V52" s="2"/>
+    </row>
+    <row r="53" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N53" t="s">
+        <v>164</v>
+      </c>
+      <c r="P53" t="s">
+        <v>174</v>
+      </c>
+      <c r="R53" t="s">
+        <v>182</v>
+      </c>
+      <c r="U53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N54" t="s">
+        <v>165</v>
+      </c>
+      <c r="P54" t="s">
+        <v>175</v>
+      </c>
+      <c r="R54" t="s">
+        <v>183</v>
+      </c>
+      <c r="U54" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="55" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N55" t="s">
+        <v>166</v>
+      </c>
+      <c r="P55" t="s">
+        <v>176</v>
+      </c>
+      <c r="R55" t="s">
+        <v>184</v>
+      </c>
+      <c r="U55" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N56" t="s">
+        <v>167</v>
+      </c>
+      <c r="P56" t="s">
+        <v>177</v>
+      </c>
+      <c r="R56" t="s">
+        <v>185</v>
+      </c>
+      <c r="U56" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="57" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N57" t="s">
+        <v>168</v>
+      </c>
+      <c r="P57" t="s">
+        <v>178</v>
+      </c>
+      <c r="R57" t="s">
+        <v>186</v>
+      </c>
+      <c r="U57" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="58" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N58" t="s">
+        <v>169</v>
+      </c>
+      <c r="P58" t="s">
+        <v>179</v>
+      </c>
+      <c r="R58" t="s">
+        <v>187</v>
+      </c>
+      <c r="U58" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="59" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N59" t="s">
+        <v>128</v>
+      </c>
+      <c r="P59" t="s">
+        <v>180</v>
+      </c>
+      <c r="U59" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N60" t="s">
+        <v>170</v>
+      </c>
+      <c r="U60" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N61" t="s">
+        <v>171</v>
+      </c>
+      <c r="U61" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="62" spans="14:22" x14ac:dyDescent="0.25">
+      <c r="N62" t="s">
+        <v>172</v>
+      </c>
+      <c r="U62" t="s">
+        <v>68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
